--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91890E17-46EC-4E9F-B303-A845406D3965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC0D9CE-434C-4BE5-AA69-BBB8272CBFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="680">
   <si>
     <t>taxon</t>
   </si>
@@ -148,9 +148,6 @@
     <t>Cyclosa oculata</t>
   </si>
   <si>
-    <t>Gibbaranea</t>
-  </si>
-  <si>
     <t>Gibbaranea gibbosa</t>
   </si>
   <si>
@@ -217,9 +214,6 @@
     <t>Cheiracanthium elegans</t>
   </si>
   <si>
-    <t>Cheiracanthium</t>
-  </si>
-  <si>
     <t>Cheiracanthium mildei</t>
   </si>
   <si>
@@ -286,18 +280,12 @@
     <t>Clubiona trivialis</t>
   </si>
   <si>
-    <t>Porrhoclubiona</t>
-  </si>
-  <si>
     <t>Porrhoclubiona leucaspis</t>
   </si>
   <si>
     <t>Cryphoeca silvicola</t>
   </si>
   <si>
-    <t>Archaeodictyna</t>
-  </si>
-  <si>
     <t>Argenna patula</t>
   </si>
   <si>
@@ -406,9 +394,6 @@
     <t>Haplodrassus cognatus</t>
   </si>
   <si>
-    <t>Haplodrassus</t>
-  </si>
-  <si>
     <t>Haplodrassus kulczynskii</t>
   </si>
   <si>
@@ -457,9 +442,6 @@
     <t>Phaeocedus braccatus</t>
   </si>
   <si>
-    <t>Poecilochroa</t>
-  </si>
-  <si>
     <t>Poecilochroa variana</t>
   </si>
   <si>
@@ -574,9 +556,6 @@
     <t>Baryphyma trifrons</t>
   </si>
   <si>
-    <t>Bathyphantes</t>
-  </si>
-  <si>
     <t>Bathyphantes gracilis</t>
   </si>
   <si>
@@ -709,9 +688,6 @@
     <t>Gonatium rubens</t>
   </si>
   <si>
-    <t>Gongylidiellum</t>
-  </si>
-  <si>
     <t>Gongylidiellum vivum</t>
   </si>
   <si>
@@ -724,9 +700,6 @@
     <t>Hylyphantes nigritus</t>
   </si>
   <si>
-    <t>Hypomma</t>
-  </si>
-  <si>
     <t>Hypomma cornutum</t>
   </si>
   <si>
@@ -769,9 +742,6 @@
     <t>Macrargus rufus</t>
   </si>
   <si>
-    <t>Mansuphantes</t>
-  </si>
-  <si>
     <t>Maso gallicus</t>
   </si>
   <si>
@@ -781,24 +751,15 @@
     <t>Mecopisthes silus</t>
   </si>
   <si>
-    <t>Megalepthyphantes</t>
-  </si>
-  <si>
     <t>Mermessus trilobatus</t>
   </si>
   <si>
-    <t>Metopobactrus</t>
-  </si>
-  <si>
     <t>Micrargus herbigradus</t>
   </si>
   <si>
     <t>Micrargus subaequalis</t>
   </si>
   <si>
-    <t>Microctenonyx</t>
-  </si>
-  <si>
     <t>Microlinyphia impigra</t>
   </si>
   <si>
@@ -823,15 +784,9 @@
     <t>Moebelia penicillata</t>
   </si>
   <si>
-    <t>Monocephalus</t>
-  </si>
-  <si>
     <t>Monocephalus fuscipes</t>
   </si>
   <si>
-    <t>Nematogmus</t>
-  </si>
-  <si>
     <t>Neriene clathrata</t>
   </si>
   <si>
@@ -895,9 +850,6 @@
     <t>Panamomops sulcifrons</t>
   </si>
   <si>
-    <t>Parapelecopsis</t>
-  </si>
-  <si>
     <t>Pelecopsis parallela</t>
   </si>
   <si>
@@ -925,9 +877,6 @@
     <t>Porrhomma egeria</t>
   </si>
   <si>
-    <t>Porrhomma</t>
-  </si>
-  <si>
     <t>Porrhomma oblitum</t>
   </si>
   <si>
@@ -937,9 +886,6 @@
     <t>Prinerigone vagans</t>
   </si>
   <si>
-    <t>Pseudomaro</t>
-  </si>
-  <si>
     <t>Saaristoa abnormis</t>
   </si>
   <si>
@@ -1003,9 +949,6 @@
     <t>Tenuiphantes mengei</t>
   </si>
   <si>
-    <t>Tenuiphantes</t>
-  </si>
-  <si>
     <t>Tenuiphantes tenuis</t>
   </si>
   <si>
@@ -1015,9 +958,6 @@
     <t>Tiso vagans</t>
   </si>
   <si>
-    <t>Trematocephalus</t>
-  </si>
-  <si>
     <t>Trichoncus affinis</t>
   </si>
   <si>
@@ -1033,9 +973,6 @@
     <t>Trichopternoides thorelli</t>
   </si>
   <si>
-    <t>Troglohyphantes</t>
-  </si>
-  <si>
     <t>Troxochrus scabriculus</t>
   </si>
   <si>
@@ -1054,9 +991,6 @@
     <t>Walckenaeria capito</t>
   </si>
   <si>
-    <t>Walckenaeria</t>
-  </si>
-  <si>
     <t>Walckenaeria cucullata</t>
   </si>
   <si>
@@ -1159,9 +1093,6 @@
     <t>Hogna radiata</t>
   </si>
   <si>
-    <t>Hygrolycosa</t>
-  </si>
-  <si>
     <t>Pardosa agrestis</t>
   </si>
   <si>
@@ -1273,9 +1204,6 @@
     <t>Nesticus cellulanus</t>
   </si>
   <si>
-    <t>Ischnothyreus</t>
-  </si>
-  <si>
     <t>Oonops domesticus</t>
   </si>
   <si>
@@ -1288,9 +1216,6 @@
     <t>Triaeris stenaspis</t>
   </si>
   <si>
-    <t>Oxyopes</t>
-  </si>
-  <si>
     <t>Oxyopes lineatus</t>
   </si>
   <si>
@@ -1315,9 +1240,6 @@
     <t>Philodromus dispar</t>
   </si>
   <si>
-    <t>Philodromus</t>
-  </si>
-  <si>
     <t>Philodromus longipalpis</t>
   </si>
   <si>
@@ -1333,9 +1255,6 @@
     <t>Philodromus rufus</t>
   </si>
   <si>
-    <t>Pulchellodromus</t>
-  </si>
-  <si>
     <t>Rhysodromus histrio</t>
   </si>
   <si>
@@ -1411,9 +1330,6 @@
     <t>Ballus rufipes</t>
   </si>
   <si>
-    <t>Carrhotus</t>
-  </si>
-  <si>
     <t>Chalcoscirtus infimus</t>
   </si>
   <si>
@@ -1459,9 +1375,6 @@
     <t>Icius subinermis</t>
   </si>
   <si>
-    <t>Leptorchestes</t>
-  </si>
-  <si>
     <t>Marpissa muscosa</t>
   </si>
   <si>
@@ -1666,9 +1579,6 @@
     <t>Enoplognatha ovata</t>
   </si>
   <si>
-    <t>Enoplognatha</t>
-  </si>
-  <si>
     <t>Enoplognatha mordax</t>
   </si>
   <si>
@@ -1696,9 +1606,6 @@
     <t>Euryopis quinqueguttata</t>
   </si>
   <si>
-    <t>Heterotheridion</t>
-  </si>
-  <si>
     <t>Kochiura aulica</t>
   </si>
   <si>
@@ -1723,9 +1630,6 @@
     <t>Parasteatoda simulans</t>
   </si>
   <si>
-    <t>Parasteatoda</t>
-  </si>
-  <si>
     <t>Pholcomma gibbum</t>
   </si>
   <si>
@@ -1810,9 +1714,6 @@
     <t>Theridion varians</t>
   </si>
   <si>
-    <t>Theridiosoma</t>
-  </si>
-  <si>
     <t>Bassaniodes robustus</t>
   </si>
   <si>
@@ -2020,10 +1921,145 @@
     <t>www/media/zilla_diodia_male.webp</t>
   </si>
   <si>
+    <t>www/media/cheiracanthium_mildei_male.webp</t>
+  </si>
+  <si>
     <t>www/media/zilla_diodia_femelle.webp</t>
   </si>
   <si>
     <t>www/media/zygiella_x-notata.webp</t>
+  </si>
+  <si>
+    <t>www/media/cheiracanthium_femelle.webp</t>
+  </si>
+  <si>
+    <t>Gibbaranea bituberculata</t>
+  </si>
+  <si>
+    <t>Cheiracanthium erraticum</t>
+  </si>
+  <si>
+    <t>Cheiracanthium punctorium</t>
+  </si>
+  <si>
+    <t>Cheiracanthium virescens</t>
+  </si>
+  <si>
+    <t>Porrhoclubiona genevensis</t>
+  </si>
+  <si>
+    <t>Archaeodictyna ammophila</t>
+  </si>
+  <si>
+    <t>Haplodrassus dalmatensis</t>
+  </si>
+  <si>
+    <t>Poecilochroa albomaculata</t>
+  </si>
+  <si>
+    <t>Bathyphantes approximatus</t>
+  </si>
+  <si>
+    <t>Gongylidiellum latebricola</t>
+  </si>
+  <si>
+    <t>Gongylidiellum murcidum</t>
+  </si>
+  <si>
+    <t>Hypomma bituberculatum</t>
+  </si>
+  <si>
+    <t>Mansuphantes mansuetus</t>
+  </si>
+  <si>
+    <t>Megalepthyphantes nebulosus</t>
+  </si>
+  <si>
+    <t>Metopobactrus prominulus</t>
+  </si>
+  <si>
+    <t>Microctenonyx subitaneus</t>
+  </si>
+  <si>
+    <t>Monocephalus castaneipes</t>
+  </si>
+  <si>
+    <t>Nematogmus sanguinolentus</t>
+  </si>
+  <si>
+    <t>Parapelecopsis nemoralis</t>
+  </si>
+  <si>
+    <t>Porrhomma microphthalmum</t>
+  </si>
+  <si>
+    <t>Pseudomaro aenigmaticus</t>
+  </si>
+  <si>
+    <t>Tenuiphantes tenebricola</t>
+  </si>
+  <si>
+    <t>Tenuiphantes zimmermanni</t>
+  </si>
+  <si>
+    <t>Trematocephalus cristatus</t>
+  </si>
+  <si>
+    <t>Troglohyphantes lucifuga</t>
+  </si>
+  <si>
+    <t>Walckenaeria corniculans</t>
+  </si>
+  <si>
+    <t>Walckenaeria dysderoides</t>
+  </si>
+  <si>
+    <t>Walckenaeria monoceros</t>
+  </si>
+  <si>
+    <t>Hygrolycosa rubrofasciata</t>
+  </si>
+  <si>
+    <t>Ischnothyreus lymphaseus</t>
+  </si>
+  <si>
+    <t>Oxyopes heterophthalmus</t>
+  </si>
+  <si>
+    <t>Philodromus emarginatus</t>
+  </si>
+  <si>
+    <t>Philodromus margaritatus</t>
+  </si>
+  <si>
+    <t>Pulchellodromus bistigma</t>
+  </si>
+  <si>
+    <t>Pulchellodromus pulchellus</t>
+  </si>
+  <si>
+    <t>Carrhotus xanthogramma</t>
+  </si>
+  <si>
+    <t>Leptorchestes berolinensis</t>
+  </si>
+  <si>
+    <t>Enoplognatha mandibularis</t>
+  </si>
+  <si>
+    <t>Heterotheridion nigrovariegatum</t>
+  </si>
+  <si>
+    <t>Parasteatoda tepidariorum</t>
+  </si>
+  <si>
+    <t>Theridiosoma gemmosum</t>
+  </si>
+  <si>
+    <t>www/media/clubiona_comta.webp</t>
+  </si>
+  <si>
+    <t>www/media/porrhoclubiona_leucaspis.webp</t>
   </si>
 </sst>
 </file>
@@ -2431,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
       <c r="C1" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>654</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2540,7 +2576,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>655</v>
+        <v>622</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2553,7 +2589,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>656</v>
+        <v>623</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2591,7 +2627,7 @@
         <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>650</v>
+        <v>617</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2599,7 +2635,7 @@
         <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>651</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,10 +2643,10 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>652</v>
+        <v>619</v>
       </c>
       <c r="C32" t="s">
-        <v>653</v>
+        <v>620</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2643,7 +2679,7 @@
         <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>657</v>
+        <v>624</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,7 +2687,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>658</v>
+        <v>625</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2659,7 +2695,7 @@
         <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2669,84 +2705,84 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>661</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>662</v>
+        <v>629</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>663</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2756,3016 +2792,3028 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>664</v>
+        <v>631</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>665</v>
+        <v>632</v>
       </c>
       <c r="C60" t="s">
-        <v>666</v>
+        <v>634</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>667</v>
+        <v>635</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B67" t="s">
+        <v>633</v>
+      </c>
+      <c r="C67" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="C73" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>79</v>
       </c>
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="C92" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>643</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>145</v>
+        <v>644</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>184</v>
+        <v>645</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>229</v>
+        <v>646</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>229</v>
+        <v>647</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>234</v>
+        <v>648</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>249</v>
+        <v>649</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>253</v>
+        <v>650</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>255</v>
+        <v>651</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>258</v>
+        <v>652</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>267</v>
+        <v>653</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>269</v>
+        <v>654</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>291</v>
+        <v>655</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>301</v>
+        <v>656</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>305</v>
+        <v>657</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>327</v>
+        <v>658</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>327</v>
+        <v>659</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>331</v>
+        <v>660</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>337</v>
+        <v>661</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>344</v>
+        <v>662</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>344</v>
+        <v>663</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>344</v>
+        <v>664</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>379</v>
+        <v>665</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>405</v>
+        <v>382</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>417</v>
+        <v>666</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>422</v>
+        <v>667</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>431</v>
+        <v>668</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>431</v>
+        <v>669</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>437</v>
+        <v>670</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>437</v>
+        <v>671</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>463</v>
+        <v>672</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>469</v>
+        <v>441</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>472</v>
+        <v>444</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>473</v>
+        <v>445</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>474</v>
+        <v>446</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>476</v>
+        <v>448</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>478</v>
+        <v>450</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>479</v>
+        <v>673</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>466</v>
+        <v>438</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>486</v>
+        <v>457</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>489</v>
+        <v>460</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>490</v>
+        <v>461</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>491</v>
+        <v>462</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>495</v>
+        <v>466</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>496</v>
+        <v>467</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>497</v>
+        <v>468</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>498</v>
+        <v>469</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>500</v>
+        <v>471</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>501</v>
+        <v>472</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>502</v>
+        <v>473</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>503</v>
+        <v>474</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>504</v>
+        <v>475</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>505</v>
+        <v>476</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>515</v>
+        <v>486</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>517</v>
+        <v>488</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
     </row>
     <row r="531" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
     </row>
     <row r="532" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
     </row>
     <row r="533" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
     </row>
     <row r="534" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
     </row>
     <row r="535" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
     </row>
     <row r="536" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
     </row>
     <row r="537" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
     </row>
     <row r="538" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
     </row>
     <row r="539" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
     </row>
     <row r="540" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
     </row>
     <row r="541" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
     </row>
     <row r="542" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="543" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
     </row>
     <row r="544" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
     </row>
     <row r="545" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
     </row>
     <row r="546" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
     </row>
     <row r="547" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
     </row>
     <row r="548" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
     </row>
     <row r="549" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
     </row>
     <row r="550" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
     </row>
     <row r="551" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>541</v>
+        <v>512</v>
       </c>
     </row>
     <row r="552" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>542</v>
+        <v>513</v>
       </c>
     </row>
     <row r="553" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
     </row>
     <row r="554" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
     </row>
     <row r="555" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
     </row>
     <row r="556" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
     </row>
     <row r="557" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>548</v>
+        <v>674</v>
       </c>
     </row>
     <row r="558" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>549</v>
+        <v>519</v>
       </c>
     </row>
     <row r="559" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
     </row>
     <row r="560" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
     </row>
     <row r="561" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
     </row>
     <row r="562" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>552</v>
+        <v>522</v>
       </c>
     </row>
     <row r="563" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>553</v>
+        <v>523</v>
       </c>
     </row>
     <row r="564" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
     </row>
     <row r="565" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
     </row>
     <row r="566" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
     </row>
     <row r="567" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
     </row>
     <row r="568" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>558</v>
+        <v>675</v>
       </c>
     </row>
     <row r="569" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
     </row>
     <row r="570" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
     </row>
     <row r="571" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>561</v>
+        <v>530</v>
       </c>
     </row>
     <row r="572" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>562</v>
+        <v>531</v>
       </c>
     </row>
     <row r="573" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>563</v>
+        <v>532</v>
       </c>
     </row>
     <row r="574" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>564</v>
+        <v>533</v>
       </c>
     </row>
     <row r="575" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>565</v>
+        <v>534</v>
       </c>
     </row>
     <row r="576" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>566</v>
+        <v>535</v>
       </c>
     </row>
     <row r="577" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>567</v>
+        <v>676</v>
       </c>
     </row>
     <row r="578" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
     </row>
     <row r="579" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>569</v>
+        <v>537</v>
       </c>
     </row>
     <row r="580" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>570</v>
+        <v>538</v>
       </c>
     </row>
     <row r="581" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
     </row>
     <row r="582" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>572</v>
+        <v>540</v>
       </c>
     </row>
     <row r="583" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>573</v>
+        <v>541</v>
       </c>
     </row>
     <row r="584" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
     </row>
     <row r="585" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
     </row>
     <row r="586" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
     </row>
     <row r="587" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
     </row>
     <row r="588" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
     </row>
     <row r="589" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>579</v>
+        <v>547</v>
       </c>
     </row>
     <row r="590" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
     </row>
     <row r="591" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
     </row>
     <row r="592" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
     </row>
     <row r="593" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
     </row>
     <row r="594" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
     </row>
     <row r="595" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
     </row>
     <row r="596" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
     </row>
     <row r="597" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>587</v>
+        <v>555</v>
       </c>
     </row>
     <row r="598" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
     </row>
     <row r="599" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
     </row>
     <row r="600" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
     </row>
     <row r="601" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>591</v>
+        <v>559</v>
       </c>
     </row>
     <row r="602" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>592</v>
+        <v>560</v>
       </c>
     </row>
     <row r="603" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
     </row>
     <row r="604" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>594</v>
+        <v>562</v>
       </c>
     </row>
     <row r="605" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>595</v>
+        <v>563</v>
       </c>
     </row>
     <row r="606" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>596</v>
+        <v>677</v>
       </c>
     </row>
     <row r="607" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
     </row>
     <row r="608" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>598</v>
+        <v>565</v>
       </c>
     </row>
     <row r="609" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>599</v>
+        <v>566</v>
       </c>
     </row>
     <row r="610" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
     </row>
     <row r="611" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>601</v>
+        <v>568</v>
       </c>
     </row>
     <row r="612" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
     </row>
     <row r="613" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
     </row>
     <row r="614" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
     </row>
     <row r="615" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
     </row>
     <row r="616" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>606</v>
+        <v>573</v>
       </c>
     </row>
     <row r="617" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
     </row>
     <row r="618" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>608</v>
+        <v>575</v>
       </c>
     </row>
     <row r="619" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>609</v>
+        <v>576</v>
       </c>
     </row>
     <row r="620" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>610</v>
+        <v>577</v>
       </c>
     </row>
     <row r="621" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
     </row>
     <row r="622" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
     </row>
     <row r="623" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
     </row>
     <row r="624" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>614</v>
+        <v>581</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>616</v>
+        <v>583</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>617</v>
+        <v>584</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>620</v>
+        <v>587</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>621</v>
+        <v>588</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>622</v>
+        <v>589</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>623</v>
+        <v>590</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>624</v>
+        <v>591</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>625</v>
+        <v>592</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>626</v>
+        <v>593</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>627</v>
+        <v>594</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>628</v>
+        <v>595</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>629</v>
+        <v>596</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="C640" s="1"/>
     </row>
     <row r="641" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>631</v>
+        <v>598</v>
       </c>
     </row>
     <row r="642" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>632</v>
+        <v>599</v>
       </c>
     </row>
     <row r="643" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>633</v>
+        <v>600</v>
       </c>
     </row>
     <row r="644" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>634</v>
+        <v>601</v>
       </c>
     </row>
     <row r="645" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>635</v>
+        <v>602</v>
       </c>
     </row>
     <row r="646" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>636</v>
+        <v>603</v>
       </c>
     </row>
     <row r="647" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>637</v>
+        <v>604</v>
       </c>
     </row>
     <row r="648" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>638</v>
+        <v>605</v>
       </c>
     </row>
     <row r="649" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>639</v>
+        <v>606</v>
       </c>
     </row>
     <row r="650" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>640</v>
+        <v>607</v>
       </c>
     </row>
     <row r="651" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>641</v>
+        <v>608</v>
       </c>
     </row>
     <row r="652" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>642</v>
+        <v>609</v>
       </c>
     </row>
     <row r="653" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>643</v>
+        <v>610</v>
       </c>
     </row>
     <row r="654" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>644</v>
+        <v>611</v>
       </c>
     </row>
     <row r="655" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>645</v>
+        <v>612</v>
       </c>
     </row>
     <row r="656" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>646</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82293FEC-2514-439B-91F0-29DF54609B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01C9DE3-0856-4284-84CB-E83CD3F13BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="722">
   <si>
     <t>taxon</t>
   </si>
@@ -2148,6 +2147,45 @@
   </si>
   <si>
     <t>www/media/fiches/ballus_chalybeius_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/carrhotus_xanthogramma_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/euophrys_frontalis_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/evarcha_falcata_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/heliophanus_tribulosus_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/icius_subinermis_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/carrhotus_xanthogramma_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/evarcha_arcuata_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/heliophanus_cupreus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/heliophanus_tribulosus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/icius_subinermis_femelle.webp</t>
+  </si>
+  <si>
+    <t>fiche</t>
+  </si>
+  <si>
+    <t>www/media/fiches/macaroeris_nidicolens_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/macaroeris_nidicolens_male.webp</t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2245,11 @@
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2221,8 +2263,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5221C8D7-EF93-417B-B8B8-217FC377064B}" name="Tableau1" displayName="Tableau1" ref="A1:D656" totalsRowShown="0">
-  <autoFilter ref="A1:D656" xr:uid="{5221C8D7-EF93-417B-B8B8-217FC377064B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5221C8D7-EF93-417B-B8B8-217FC377064B}" name="Tableau1" displayName="Tableau1" ref="A1:E656" totalsRowShown="0">
+  <autoFilter ref="A1:E656" xr:uid="{5221C8D7-EF93-417B-B8B8-217FC377064B}">
     <filterColumn colId="1">
       <filters>
         <filter val="?"/>
@@ -2230,11 +2272,14 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="4">
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8CF3FEBE-EC73-416E-8610-F705B8D6D336}" name="taxon"/>
     <tableColumn id="4" xr3:uid="{666FCC22-DD53-4830-B712-02B264DDA363}" name="id à vue"/>
     <tableColumn id="3" xr3:uid="{84160676-7B2A-4A0C-94B1-2901F12B1A91}" name="femelle"/>
     <tableColumn id="2" xr3:uid="{DBDA5D0E-A4B2-4E10-A6AF-85502F963E80}" name="male"/>
+    <tableColumn id="5" xr3:uid="{428EF79A-9172-4EA3-8B88-E246ACC4B653}" name="fiche" dataDxfId="0">
+      <calculatedColumnFormula>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2557,7 +2602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D656"/>
+  <dimension ref="A1:E656"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -2566,7 +2611,7 @@
     <col min="4" max="4" width="54.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2579,8 +2624,11 @@
       <c r="D1" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2590,152 +2638,228 @@
       <c r="C2" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E3" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E4" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E5" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E6" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E7" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E8" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E9" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E10" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E11" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E12" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E13" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E15" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E16" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2745,16 +2869,24 @@
       <c r="C21" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2764,56 +2896,84 @@
       <c r="C23" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E23" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E24" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2823,8 +2983,12 @@
       <c r="C30" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2834,8 +2998,12 @@
       <c r="C31" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2848,48 +3016,72 @@
       <c r="D32" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E32" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E33" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
       <c r="B34" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E34" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
       <c r="B35" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E35" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
       <c r="B36" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E36" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
       <c r="B37" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2899,8 +3091,12 @@
       <c r="C38" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2910,8 +3106,12 @@
       <c r="D39" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2921,24 +3121,36 @@
       <c r="C40" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>617</v>
       </c>
       <c r="B42" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2948,48 +3160,72 @@
       <c r="C43" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E43" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E45" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E46" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E47" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2999,16 +3235,24 @@
       <c r="C49" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E49" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -3018,32 +3262,48 @@
       <c r="C51" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E51" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E52" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E53" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>53</v>
       </c>
       <c r="B54" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E54" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -3053,16 +3313,24 @@
       <c r="C55" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E55" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>26</v>
       </c>
       <c r="B56" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E56" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -3072,8 +3340,12 @@
       <c r="C57" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E57" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -3081,16 +3353,24 @@
         <v>659</v>
       </c>
       <c r="C58" s="1"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E58" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
       <c r="B59" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -3103,16 +3383,24 @@
       <c r="D60" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E60" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -3122,40 +3410,60 @@
       <c r="C62" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E62" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
       <c r="B63" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E63" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E65" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>618</v>
       </c>
       <c r="B66" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>64</v>
       </c>
@@ -3168,48 +3476,72 @@
       <c r="D67" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E67" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>65</v>
       </c>
       <c r="B68" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>619</v>
       </c>
       <c r="B69" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E69" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>620</v>
       </c>
       <c r="B70" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E70" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>66</v>
       </c>
       <c r="B71" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E71" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>67</v>
       </c>
       <c r="B72" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>68</v>
       </c>
@@ -3219,72 +3551,108 @@
       <c r="C73" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>69</v>
       </c>
       <c r="B74" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E74" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E75" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>71</v>
       </c>
       <c r="B76" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E76" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>72</v>
       </c>
       <c r="B77" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E77" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>73</v>
       </c>
       <c r="B78" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E78" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>74</v>
       </c>
       <c r="B79" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E79" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>75</v>
       </c>
       <c r="B80" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E80" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>76</v>
       </c>
       <c r="B81" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E81" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>77</v>
       </c>
@@ -3292,80 +3660,120 @@
         <v>660</v>
       </c>
       <c r="D82" s="1"/>
-    </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E82" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>78</v>
       </c>
       <c r="B83" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E83" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>79</v>
       </c>
       <c r="B84" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E84" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>80</v>
       </c>
       <c r="B85" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E85" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>81</v>
       </c>
       <c r="B86" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E86" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>82</v>
       </c>
       <c r="B87" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E87" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>83</v>
       </c>
       <c r="B88" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E88" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>84</v>
       </c>
       <c r="B89" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E89" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>85</v>
       </c>
       <c r="B90" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E90" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>621</v>
       </c>
       <c r="B91" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E91" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>86</v>
       </c>
@@ -3375,48 +3783,72 @@
       <c r="C92" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E92" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>87</v>
       </c>
       <c r="B93" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E93" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>622</v>
       </c>
       <c r="B94" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E94" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>88</v>
       </c>
       <c r="B95" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E95" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>89</v>
       </c>
       <c r="B96" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>90</v>
       </c>
       <c r="B97" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>91</v>
       </c>
@@ -3426,56 +3858,84 @@
       <c r="D98" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E98" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>92</v>
       </c>
       <c r="B99" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E99" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>93</v>
       </c>
       <c r="B100" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E100" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>94</v>
       </c>
       <c r="B101" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E101" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>95</v>
       </c>
       <c r="B102" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E102" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>96</v>
       </c>
       <c r="B103" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E103" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>97</v>
       </c>
       <c r="B104" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E104" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>98</v>
       </c>
@@ -3488,16 +3948,24 @@
       <c r="D105" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E105" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>99</v>
       </c>
       <c r="B106" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E106" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>100</v>
       </c>
@@ -3507,8 +3975,12 @@
       <c r="C107" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E107" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>101</v>
       </c>
@@ -3518,24 +3990,36 @@
       <c r="C108" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E108" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>102</v>
       </c>
       <c r="B109" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E109" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>103</v>
       </c>
       <c r="B110" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E110" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>104</v>
       </c>
@@ -3545,16 +4029,24 @@
       <c r="D111" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E111" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>105</v>
       </c>
       <c r="B112" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E112" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>106</v>
       </c>
@@ -3564,904 +4056,1356 @@
       <c r="D113" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E113" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>107</v>
       </c>
       <c r="B114" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E114" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>109</v>
       </c>
       <c r="B115" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E115" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>110</v>
       </c>
       <c r="B116" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E116" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>111</v>
       </c>
       <c r="B117" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E117" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>112</v>
       </c>
       <c r="B118" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E118" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>113</v>
       </c>
       <c r="B119" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E119" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>114</v>
       </c>
       <c r="B120" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E120" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>115</v>
       </c>
       <c r="B121" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E121" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>116</v>
       </c>
       <c r="B122" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E122" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>117</v>
       </c>
       <c r="B123" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E123" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>118</v>
       </c>
       <c r="B124" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E124" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>119</v>
       </c>
       <c r="B125" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E125" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>120</v>
       </c>
       <c r="B126" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E126" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>121</v>
       </c>
       <c r="B127" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E127" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>122</v>
       </c>
       <c r="B128" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E128" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>123</v>
       </c>
       <c r="B129" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E129" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>623</v>
       </c>
       <c r="B130" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E130" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>124</v>
       </c>
       <c r="B131" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E131" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>125</v>
       </c>
       <c r="B132" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E132" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>126</v>
       </c>
       <c r="B133" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E133" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>127</v>
       </c>
       <c r="B134" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E134" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>128</v>
       </c>
       <c r="B135" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E135" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>129</v>
       </c>
       <c r="B136" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E136" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>130</v>
       </c>
       <c r="B137" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E137" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>131</v>
       </c>
       <c r="B138" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E138" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>132</v>
       </c>
       <c r="B139" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E139" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>133</v>
       </c>
       <c r="B140" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E140" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>134</v>
       </c>
       <c r="B141" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E141" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>135</v>
       </c>
       <c r="B142" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E142" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>136</v>
       </c>
       <c r="B143" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E143" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>137</v>
       </c>
       <c r="B144" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E144" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>138</v>
       </c>
       <c r="B145" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E145" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>108</v>
       </c>
       <c r="B146" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E146" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>139</v>
       </c>
       <c r="B147" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E147" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>624</v>
       </c>
       <c r="B148" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E148" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>140</v>
       </c>
       <c r="B149" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E149" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>141</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E150" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>142</v>
       </c>
       <c r="B151" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E151" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>143</v>
       </c>
       <c r="B152" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E152" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>144</v>
       </c>
       <c r="B153" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E153" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>145</v>
       </c>
       <c r="B154" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E154" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>146</v>
       </c>
       <c r="B155" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E155" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>147</v>
       </c>
       <c r="B156" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E156" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>148</v>
       </c>
       <c r="B157" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E157" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>149</v>
       </c>
       <c r="B158" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E158" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>150</v>
       </c>
       <c r="B159" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E159" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>151</v>
       </c>
       <c r="B160" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E160" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>152</v>
       </c>
       <c r="B161" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E161" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>153</v>
       </c>
       <c r="B162" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E162" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>154</v>
       </c>
       <c r="B163" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E163" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>155</v>
       </c>
       <c r="B164" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E164" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>156</v>
       </c>
       <c r="B165" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E165" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>157</v>
       </c>
       <c r="B166" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E166" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>158</v>
       </c>
       <c r="B167" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E167" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>159</v>
       </c>
       <c r="B168" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E168" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>160</v>
       </c>
       <c r="B169" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E169" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>161</v>
       </c>
       <c r="B170" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E170" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>162</v>
       </c>
       <c r="B171" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E171" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>163</v>
       </c>
       <c r="B172" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E172" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>164</v>
       </c>
       <c r="B173" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E173" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>165</v>
       </c>
       <c r="B174" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E174" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>166</v>
       </c>
       <c r="B175" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E175" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>167</v>
       </c>
       <c r="B176" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E176" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>168</v>
       </c>
       <c r="B177" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E177" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>169</v>
       </c>
       <c r="B178" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E178" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>170</v>
       </c>
       <c r="B179" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E179" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>171</v>
       </c>
       <c r="B180" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E180" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>172</v>
       </c>
       <c r="B181" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E181" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>173</v>
       </c>
       <c r="B182" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E182" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>174</v>
       </c>
       <c r="B183" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E183" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>175</v>
       </c>
       <c r="B184" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E184" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>176</v>
       </c>
       <c r="B185" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E185" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>177</v>
       </c>
       <c r="B186" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E186" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>625</v>
       </c>
       <c r="B187" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E187" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>178</v>
       </c>
       <c r="B188" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E188" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>179</v>
       </c>
       <c r="B189" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E189" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>180</v>
       </c>
       <c r="B190" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E190" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>181</v>
       </c>
       <c r="B191" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E191" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>182</v>
       </c>
       <c r="B192" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E192" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>183</v>
       </c>
       <c r="B193" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="194" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E193" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>184</v>
       </c>
       <c r="B194" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E194" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>185</v>
       </c>
       <c r="B195" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E195" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>186</v>
       </c>
       <c r="B196" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E196" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>187</v>
       </c>
       <c r="B197" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="198" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E197" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>188</v>
       </c>
       <c r="B198" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E198" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>189</v>
       </c>
       <c r="B199" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E199" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>190</v>
       </c>
       <c r="B200" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E200" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>191</v>
       </c>
       <c r="B201" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E201" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>192</v>
       </c>
       <c r="B202" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E202" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>193</v>
       </c>
       <c r="B203" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="204" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E203" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>194</v>
       </c>
       <c r="B204" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="205" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E204" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>195</v>
       </c>
       <c r="B205" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="206" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E205" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>196</v>
       </c>
       <c r="B206" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="207" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E206" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>197</v>
       </c>
       <c r="B207" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E207" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>198</v>
       </c>
       <c r="B208" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E208" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>199</v>
       </c>
       <c r="B209" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E209" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>200</v>
       </c>
       <c r="B210" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="211" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E210" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>201</v>
       </c>
       <c r="B211" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="212" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E211" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>202</v>
       </c>
       <c r="B212" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="213" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E212" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>203</v>
       </c>
       <c r="B213" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="214" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E213" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>204</v>
       </c>
       <c r="B214" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="215" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E214" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>205</v>
       </c>
       <c r="B215" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="216" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E215" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>206</v>
       </c>
       <c r="B216" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="217" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E216" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>207</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="218" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E217" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>208</v>
       </c>
       <c r="B218" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="219" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E218" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>209</v>
       </c>
       <c r="B219" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="220" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E219" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>210</v>
       </c>
       <c r="B220" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="221" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E220" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>211</v>
       </c>
       <c r="B221" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="222" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E221" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>212</v>
       </c>
       <c r="B222" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="223" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E222" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>213</v>
       </c>
       <c r="B223" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="224" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E223" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>214</v>
       </c>
       <c r="B224" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E224" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>215</v>
       </c>
       <c r="B225" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E225" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>216</v>
       </c>
@@ -4471,192 +5415,288 @@
       <c r="D226" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E226" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>217</v>
       </c>
       <c r="B227" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E227" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>218</v>
       </c>
       <c r="B228" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E228" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>219</v>
       </c>
       <c r="B229" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E229" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>220</v>
       </c>
       <c r="B230" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E230" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>221</v>
       </c>
       <c r="B231" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E231" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>626</v>
       </c>
       <c r="B232" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E232" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>627</v>
       </c>
       <c r="B233" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E233" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>222</v>
       </c>
       <c r="B234" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E234" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>223</v>
       </c>
       <c r="B235" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E235" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>224</v>
       </c>
       <c r="B236" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E236" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>225</v>
       </c>
       <c r="B237" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E237" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>628</v>
       </c>
       <c r="B238" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E238" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>226</v>
       </c>
       <c r="B239" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E239" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>227</v>
       </c>
       <c r="B240" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E240" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>228</v>
       </c>
       <c r="B241" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E241" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>229</v>
       </c>
       <c r="B242" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E242" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>230</v>
       </c>
       <c r="B243" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E243" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>231</v>
       </c>
       <c r="B244" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E244" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>232</v>
       </c>
       <c r="B245" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E245" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>233</v>
       </c>
       <c r="B246" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E246" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>234</v>
       </c>
       <c r="B247" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E247" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>235</v>
       </c>
       <c r="B248" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E248" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>236</v>
       </c>
       <c r="B249" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E249" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>237</v>
       </c>
@@ -4669,224 +5709,336 @@
       <c r="D250" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E250" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>238</v>
       </c>
       <c r="B251" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E251" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>239</v>
       </c>
       <c r="B252" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E252" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>629</v>
       </c>
       <c r="B253" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E253" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>240</v>
       </c>
       <c r="B254" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E254" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>241</v>
       </c>
       <c r="B255" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E255" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>242</v>
       </c>
       <c r="B256" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="257" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E256" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>630</v>
       </c>
       <c r="B257" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="258" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E257" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>243</v>
       </c>
       <c r="B258" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="259" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E258" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>631</v>
       </c>
       <c r="B259" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="260" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E259" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>244</v>
       </c>
       <c r="B260" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="261" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E260" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>245</v>
       </c>
       <c r="B261" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="262" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E261" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>632</v>
       </c>
       <c r="B262" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="263" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E262" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>246</v>
       </c>
       <c r="B263" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="264" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E263" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>247</v>
       </c>
       <c r="B264" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="265" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E264" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>248</v>
       </c>
       <c r="B265" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="266" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E265" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>249</v>
       </c>
       <c r="B266" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="267" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E266" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>250</v>
       </c>
       <c r="B267" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="268" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E267" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>251</v>
       </c>
       <c r="B268" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="269" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E268" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>252</v>
       </c>
       <c r="B269" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="270" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E269" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>253</v>
       </c>
       <c r="B270" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="271" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E270" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>633</v>
       </c>
       <c r="B271" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="272" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E271" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>254</v>
       </c>
       <c r="B272" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E272" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>634</v>
       </c>
       <c r="B273" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E273" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>255</v>
       </c>
       <c r="B274" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E274" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>256</v>
       </c>
       <c r="B275" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E275" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>257</v>
       </c>
       <c r="B276" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E276" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>258</v>
       </c>
       <c r="B277" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E277" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>259</v>
       </c>
@@ -4896,16 +6048,24 @@
       <c r="D278" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E278" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>260</v>
       </c>
       <c r="B279" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E279" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>261</v>
       </c>
@@ -4918,56 +6078,84 @@
       <c r="D280" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E280" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>262</v>
       </c>
       <c r="B281" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E281" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>263</v>
       </c>
       <c r="B282" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E282" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>264</v>
       </c>
       <c r="B283" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E283" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>265</v>
       </c>
       <c r="B284" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E284" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>266</v>
       </c>
       <c r="B285" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E285" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>267</v>
       </c>
       <c r="B286" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E286" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>268</v>
       </c>
@@ -4977,784 +6165,1176 @@
       <c r="C287" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E287" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>269</v>
       </c>
       <c r="B288" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="289" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E288" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>270</v>
       </c>
       <c r="B289" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="290" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E289" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>271</v>
       </c>
       <c r="B290" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="291" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E290" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>272</v>
       </c>
       <c r="B291" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="292" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E291" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>273</v>
       </c>
       <c r="B292" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="293" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E292" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>274</v>
       </c>
       <c r="B293" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="294" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E293" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>275</v>
       </c>
       <c r="B294" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="295" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E294" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>635</v>
       </c>
       <c r="B295" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="296" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E295" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>276</v>
       </c>
       <c r="B296" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="297" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E296" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>277</v>
       </c>
       <c r="B297" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="298" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E297" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>278</v>
       </c>
       <c r="B298" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="299" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E298" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>279</v>
       </c>
       <c r="B299" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="300" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E299" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>280</v>
       </c>
       <c r="B300" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="301" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E300" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>281</v>
       </c>
       <c r="B301" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="302" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E301" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>282</v>
       </c>
       <c r="B302" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="303" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E302" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>283</v>
       </c>
       <c r="B303" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="304" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E303" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>284</v>
       </c>
       <c r="B304" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="305" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E304" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>636</v>
       </c>
       <c r="B305" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="306" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E305" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>285</v>
       </c>
       <c r="B306" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="307" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E306" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>286</v>
       </c>
       <c r="B307" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="308" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E307" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>287</v>
       </c>
       <c r="B308" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="309" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E308" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>637</v>
       </c>
       <c r="B309" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="310" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E309" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>288</v>
       </c>
       <c r="B310" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="311" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E310" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>289</v>
       </c>
       <c r="B311" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="312" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E311" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>290</v>
       </c>
       <c r="B312" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="313" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E312" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>291</v>
       </c>
       <c r="B313" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="314" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E313" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>292</v>
       </c>
       <c r="B314" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="315" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E314" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>293</v>
       </c>
       <c r="B315" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="316" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E315" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>294</v>
       </c>
       <c r="B316" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="317" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E316" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>295</v>
       </c>
       <c r="B317" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="318" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E317" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>296</v>
       </c>
       <c r="B318" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="319" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E318" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>297</v>
       </c>
       <c r="B319" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="320" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E319" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>298</v>
       </c>
       <c r="B320" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="321" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E320" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>299</v>
       </c>
       <c r="B321" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="322" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E321" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>300</v>
       </c>
       <c r="B322" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="323" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E322" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>301</v>
       </c>
       <c r="B323" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="324" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E323" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>302</v>
       </c>
       <c r="B324" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="325" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E324" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>303</v>
       </c>
       <c r="B325" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="326" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E325" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>304</v>
       </c>
       <c r="B326" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="327" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E326" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>305</v>
       </c>
       <c r="B327" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="328" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E327" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>306</v>
       </c>
       <c r="B328" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="329" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E328" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>307</v>
       </c>
       <c r="B329" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="330" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E329" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>308</v>
       </c>
       <c r="B330" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="331" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E330" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>638</v>
       </c>
       <c r="B331" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="332" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E331" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>309</v>
       </c>
       <c r="B332" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="333" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E332" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>639</v>
       </c>
       <c r="B333" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="334" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E333" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>310</v>
       </c>
       <c r="B334" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="335" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E334" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>614</v>
       </c>
       <c r="B335" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="336" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E335" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>311</v>
       </c>
       <c r="B336" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="337" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E336" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>640</v>
       </c>
       <c r="B337" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="338" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E337" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>312</v>
       </c>
       <c r="B338" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="339" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E338" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>313</v>
       </c>
       <c r="B339" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="340" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E339" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>314</v>
       </c>
       <c r="B340" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="341" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E340" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>315</v>
       </c>
       <c r="B341" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="342" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E341" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>316</v>
       </c>
       <c r="B342" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="343" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E342" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>641</v>
       </c>
       <c r="B343" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="344" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E343" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>317</v>
       </c>
       <c r="B344" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E344" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>318</v>
       </c>
       <c r="B345" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="346" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E345" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>319</v>
       </c>
       <c r="B346" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="347" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E346" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>320</v>
       </c>
       <c r="B347" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="348" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E347" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>321</v>
       </c>
       <c r="B348" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="349" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E348" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>322</v>
       </c>
       <c r="B349" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="350" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E349" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>642</v>
       </c>
       <c r="B350" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="351" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E350" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>323</v>
       </c>
       <c r="B351" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="352" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E351" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>324</v>
       </c>
       <c r="B352" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="353" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E352" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>643</v>
       </c>
       <c r="B353" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="354" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E353" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>325</v>
       </c>
       <c r="B354" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="355" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E354" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>326</v>
       </c>
       <c r="B355" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="356" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E355" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>327</v>
       </c>
       <c r="B356" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="357" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E356" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>644</v>
       </c>
       <c r="B357" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="358" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E357" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>328</v>
       </c>
       <c r="B358" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="359" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E358" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>329</v>
       </c>
       <c r="B359" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="360" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E359" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>330</v>
       </c>
       <c r="B360" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="361" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E360" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>331</v>
       </c>
       <c r="B361" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="362" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E361" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>332</v>
       </c>
       <c r="B362" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="363" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E362" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>333</v>
       </c>
       <c r="B363" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="364" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E363" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>334</v>
       </c>
       <c r="B364" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="365" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E364" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>335</v>
       </c>
       <c r="B365" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="366" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E365" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>336</v>
       </c>
       <c r="B366" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="367" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E366" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>337</v>
       </c>
       <c r="B367" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="368" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E367" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>338</v>
       </c>
       <c r="B368" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E368" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>339</v>
       </c>
       <c r="B369" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E369" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>340</v>
       </c>
       <c r="B370" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E370" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>341</v>
       </c>
       <c r="B371" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="372" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E371" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>342</v>
       </c>
       <c r="B372" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E372" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>343</v>
       </c>
       <c r="B373" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E373" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>344</v>
       </c>
       <c r="B374" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="375" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E374" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>345</v>
       </c>
       <c r="B375" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E375" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>346</v>
       </c>
       <c r="B376" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="377" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E376" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>347</v>
       </c>
       <c r="B377" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="378" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E377" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>348</v>
       </c>
       <c r="B378" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="379" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E378" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>349</v>
       </c>
       <c r="B379" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="380" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E379" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>350</v>
       </c>
       <c r="B380" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="381" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E380" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>351</v>
       </c>
       <c r="B381" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="382" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E381" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>352</v>
       </c>
       <c r="B382" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E382" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>353</v>
       </c>
       <c r="B383" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="384" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E383" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>354</v>
       </c>
       <c r="B384" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E384" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>355</v>
       </c>
@@ -5764,424 +7344,636 @@
       <c r="D385" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E385" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>356</v>
       </c>
       <c r="B386" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E386" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>645</v>
       </c>
       <c r="B387" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E387" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>357</v>
       </c>
       <c r="B388" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E388" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>358</v>
       </c>
       <c r="B389" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E389" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>359</v>
       </c>
       <c r="B390" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E390" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>360</v>
       </c>
       <c r="B391" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E391" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>361</v>
       </c>
       <c r="B392" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E392" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>362</v>
       </c>
       <c r="B393" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E393" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>363</v>
       </c>
       <c r="B394" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E394" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>364</v>
       </c>
       <c r="B395" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E395" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>365</v>
       </c>
       <c r="B396" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E396" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>366</v>
       </c>
       <c r="B397" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E397" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>367</v>
       </c>
       <c r="B398" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E398" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>368</v>
       </c>
       <c r="B399" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E399" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>369</v>
       </c>
       <c r="B400" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="401" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E400" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>370</v>
       </c>
       <c r="B401" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="402" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E401" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>371</v>
       </c>
       <c r="B402" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E402" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>372</v>
       </c>
       <c r="B403" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="404" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E403" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>373</v>
       </c>
       <c r="B404" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="405" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E404" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>374</v>
       </c>
       <c r="B405" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="406" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E405" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>375</v>
       </c>
       <c r="B406" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="407" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E406" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>376</v>
       </c>
       <c r="B407" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="408" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E407" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>377</v>
       </c>
       <c r="B408" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="409" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E408" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>378</v>
       </c>
       <c r="B409" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="410" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E409" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>379</v>
       </c>
       <c r="B410" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="411" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E410" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>380</v>
       </c>
       <c r="B411" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="412" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E411" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>381</v>
       </c>
       <c r="B412" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E412" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>382</v>
       </c>
       <c r="B413" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="414" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E413" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>383</v>
       </c>
       <c r="B414" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="415" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E414" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>384</v>
       </c>
       <c r="B415" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="416" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E415" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>385</v>
       </c>
       <c r="B416" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="417" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E416" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>386</v>
       </c>
       <c r="B417" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="418" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E417" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>387</v>
       </c>
       <c r="B418" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="419" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E418" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>388</v>
       </c>
       <c r="B419" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E419" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>389</v>
       </c>
       <c r="B420" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="421" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E420" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>390</v>
       </c>
       <c r="B421" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="422" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E421" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>391</v>
       </c>
       <c r="B422" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E422" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>392</v>
       </c>
       <c r="B423" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E423" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>393</v>
       </c>
       <c r="B424" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="425" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E424" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>646</v>
       </c>
       <c r="B425" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="426" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E425" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>394</v>
       </c>
       <c r="B426" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="427" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E426" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>395</v>
       </c>
       <c r="B427" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="428" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E427" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>396</v>
       </c>
       <c r="B428" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="429" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E428" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>397</v>
       </c>
       <c r="B429" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E429" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>647</v>
       </c>
       <c r="B430" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="431" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E430" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>398</v>
       </c>
       <c r="B431" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="432" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E431" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>399</v>
       </c>
       <c r="B432" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E432" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>400</v>
       </c>
       <c r="B433" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E433" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>401</v>
       </c>
       <c r="B434" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E434" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>402</v>
       </c>
       <c r="B435" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E435" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>403</v>
       </c>
       <c r="B436" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E436" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>404</v>
       </c>
       <c r="B437" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E437" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>405</v>
       </c>
@@ -6194,136 +7986,204 @@
       <c r="D438" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E438" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>648</v>
       </c>
       <c r="B439" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E439" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>406</v>
       </c>
       <c r="B440" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E440" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>649</v>
       </c>
       <c r="B441" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E441" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>407</v>
       </c>
       <c r="B442" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E442" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>408</v>
       </c>
       <c r="B443" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E443" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>409</v>
       </c>
       <c r="B444" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E444" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>410</v>
       </c>
       <c r="B445" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E445" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>650</v>
       </c>
       <c r="B446" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E446" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>651</v>
       </c>
       <c r="B447" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E447" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>411</v>
       </c>
       <c r="B448" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E448" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>412</v>
       </c>
       <c r="B449" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E449" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>413</v>
       </c>
       <c r="B450" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E450" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>414</v>
       </c>
       <c r="B451" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E451" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>415</v>
       </c>
       <c r="B452" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E452" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>416</v>
       </c>
       <c r="B453" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E453" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>417</v>
       </c>
       <c r="B454" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E454" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>418</v>
       </c>
@@ -6333,16 +8193,24 @@
       <c r="C455" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E455" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>419</v>
       </c>
       <c r="B456" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E456" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>420</v>
       </c>
@@ -6355,8 +8223,12 @@
       <c r="D457" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E457" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>421</v>
       </c>
@@ -6366,48 +8238,72 @@
       <c r="D458" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E458" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>422</v>
       </c>
       <c r="B459" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E459" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>423</v>
       </c>
       <c r="B460" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E460" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>424</v>
       </c>
       <c r="B461" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E461" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>425</v>
       </c>
       <c r="B462" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E462" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>426</v>
       </c>
       <c r="B463" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E463" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>427</v>
       </c>
@@ -6420,40 +8316,60 @@
       <c r="D464" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E464" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>428</v>
       </c>
       <c r="B465" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E465" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>429</v>
       </c>
       <c r="B466" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E466" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>430</v>
       </c>
       <c r="B467" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E467" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>431</v>
       </c>
       <c r="B468" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E468" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>432</v>
       </c>
@@ -6463,16 +8379,24 @@
       <c r="D469" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E469" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>433</v>
       </c>
       <c r="B470" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E470" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>434</v>
       </c>
@@ -6482,1352 +8406,2064 @@
       <c r="D471" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E471" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>435</v>
       </c>
       <c r="B472" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E472" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>652</v>
       </c>
       <c r="B473" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C473" t="s">
+        <v>714</v>
+      </c>
+      <c r="D473" t="s">
+        <v>709</v>
+      </c>
+      <c r="E473" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>436</v>
       </c>
       <c r="B474" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E474" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>437</v>
       </c>
       <c r="B475" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E475" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>439</v>
       </c>
       <c r="B476" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D476" t="s">
+        <v>710</v>
+      </c>
+      <c r="E476" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>440</v>
       </c>
       <c r="B477" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C477" t="s">
+        <v>715</v>
+      </c>
+      <c r="E477" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>441</v>
       </c>
       <c r="B478" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D478" t="s">
+        <v>711</v>
+      </c>
+      <c r="E478" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>442</v>
       </c>
       <c r="B479" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E479" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>443</v>
       </c>
       <c r="B480" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E480" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>444</v>
       </c>
       <c r="B481" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="482" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E481" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>445</v>
       </c>
       <c r="B482" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E482" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>446</v>
       </c>
       <c r="B483" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="484" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C483" t="s">
+        <v>716</v>
+      </c>
+      <c r="E483" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>447</v>
       </c>
       <c r="B484" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E484" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>448</v>
       </c>
       <c r="B485" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E485" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>449</v>
       </c>
       <c r="B486" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C486" t="s">
+        <v>717</v>
+      </c>
+      <c r="D486" t="s">
+        <v>712</v>
+      </c>
+      <c r="E486" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>450</v>
       </c>
       <c r="B487" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C487" t="s">
+        <v>718</v>
+      </c>
+      <c r="D487" t="s">
+        <v>713</v>
+      </c>
+      <c r="E487" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>653</v>
       </c>
       <c r="B488" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E488" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>438</v>
       </c>
       <c r="B489" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C489" t="s">
+        <v>720</v>
+      </c>
+      <c r="D489" t="s">
+        <v>721</v>
+      </c>
+      <c r="E489" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>451</v>
       </c>
       <c r="B490" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E490" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>452</v>
       </c>
       <c r="B491" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="492" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E491" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>453</v>
       </c>
       <c r="B492" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="493" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E492" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>454</v>
       </c>
       <c r="B493" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E493" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>455</v>
       </c>
       <c r="B494" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E494" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>456</v>
       </c>
       <c r="B495" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="496" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E495" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>457</v>
       </c>
       <c r="B496" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="497" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E496" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>458</v>
       </c>
       <c r="B497" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="498" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E497" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>459</v>
       </c>
       <c r="B498" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="499" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E498" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>460</v>
       </c>
       <c r="B499" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="500" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E499" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>461</v>
       </c>
       <c r="B500" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E500" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>462</v>
       </c>
       <c r="B501" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E501" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>463</v>
       </c>
       <c r="B502" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E502" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>464</v>
       </c>
       <c r="B503" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E503" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>465</v>
       </c>
       <c r="B504" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E504" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>466</v>
       </c>
       <c r="B505" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="506" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E505" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>467</v>
       </c>
       <c r="B506" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="507" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E506" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>468</v>
       </c>
       <c r="B507" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E507" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>469</v>
       </c>
       <c r="B508" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E508" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>470</v>
       </c>
       <c r="B509" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="510" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E509" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>471</v>
       </c>
       <c r="B510" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="511" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E510" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>472</v>
       </c>
       <c r="B511" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E511" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>473</v>
       </c>
       <c r="B512" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E512" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>474</v>
       </c>
       <c r="B513" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="514" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E513" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>475</v>
       </c>
       <c r="B514" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="515" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E514" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>476</v>
       </c>
       <c r="B515" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="516" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E515" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>477</v>
       </c>
       <c r="B516" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="517" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E516" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>478</v>
       </c>
       <c r="B517" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="518" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E517" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>479</v>
       </c>
       <c r="B518" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E518" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>480</v>
       </c>
       <c r="B519" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="520" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E519" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>481</v>
       </c>
       <c r="B520" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="521" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E520" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>482</v>
       </c>
       <c r="B521" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E521" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>483</v>
       </c>
       <c r="B522" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E522" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>484</v>
       </c>
       <c r="B523" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E523" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>485</v>
       </c>
       <c r="B524" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E524" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>487</v>
       </c>
       <c r="B525" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E525" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>486</v>
       </c>
       <c r="B526" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E526" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>488</v>
       </c>
       <c r="B527" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E527" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>489</v>
       </c>
       <c r="B528" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E528" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>490</v>
       </c>
       <c r="B529" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E529" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>491</v>
       </c>
       <c r="B530" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E530" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>492</v>
       </c>
       <c r="B531" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E531" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>493</v>
       </c>
       <c r="B532" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E532" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>495</v>
       </c>
       <c r="B533" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E533" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>494</v>
       </c>
       <c r="B534" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E534" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>496</v>
       </c>
       <c r="B535" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E535" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>497</v>
       </c>
       <c r="B536" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E536" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>498</v>
       </c>
       <c r="B537" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="538" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E537" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>499</v>
       </c>
       <c r="B538" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="539" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E538" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>500</v>
       </c>
       <c r="B539" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="540" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E539" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>501</v>
       </c>
       <c r="B540" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="541" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E540" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>502</v>
       </c>
       <c r="B541" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="542" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E541" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>503</v>
       </c>
       <c r="B542" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="543" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E542" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>504</v>
       </c>
       <c r="B543" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="544" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E543" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>505</v>
       </c>
       <c r="B544" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="545" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E544" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>506</v>
       </c>
       <c r="B545" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="546" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E545" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>507</v>
       </c>
       <c r="B546" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E546" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>508</v>
       </c>
       <c r="B547" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E547" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>509</v>
       </c>
       <c r="B548" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="549" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E548" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>510</v>
       </c>
       <c r="B549" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="550" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E549" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>511</v>
       </c>
       <c r="B550" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="551" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E550" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>512</v>
       </c>
       <c r="B551" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E551" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>513</v>
       </c>
       <c r="B552" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="553" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E552" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>514</v>
       </c>
       <c r="B553" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="554" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E553" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>515</v>
       </c>
       <c r="B554" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="555" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E554" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>516</v>
       </c>
       <c r="B555" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="556" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E555" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>517</v>
       </c>
       <c r="B556" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="557" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E556" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>654</v>
       </c>
       <c r="B557" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="558" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E557" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>519</v>
       </c>
       <c r="B558" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="559" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E558" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>518</v>
       </c>
       <c r="B559" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="560" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E559" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>520</v>
       </c>
       <c r="B560" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="561" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E560" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>521</v>
       </c>
       <c r="B561" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E561" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>522</v>
       </c>
       <c r="B562" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E562" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>523</v>
       </c>
       <c r="B563" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E563" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>524</v>
       </c>
       <c r="B564" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E564" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>525</v>
       </c>
       <c r="B565" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="566" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E565" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>526</v>
       </c>
       <c r="B566" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="567" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E566" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>527</v>
       </c>
       <c r="B567" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="568" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E567" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>655</v>
       </c>
       <c r="B568" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E568" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>528</v>
       </c>
       <c r="B569" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="570" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E569" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>529</v>
       </c>
       <c r="B570" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E570" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>530</v>
       </c>
       <c r="B571" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E571" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>531</v>
       </c>
       <c r="B572" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="573" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E572" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>532</v>
       </c>
       <c r="B573" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="574" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E573" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>533</v>
       </c>
       <c r="B574" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E574" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>534</v>
       </c>
       <c r="B575" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E575" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>535</v>
       </c>
       <c r="B576" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E576" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>656</v>
       </c>
       <c r="B577" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="578" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E577" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>536</v>
       </c>
       <c r="B578" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E578" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>537</v>
       </c>
       <c r="B579" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="580" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E579" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>538</v>
       </c>
       <c r="B580" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="581" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E580" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>539</v>
       </c>
       <c r="B581" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="582" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E581" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>540</v>
       </c>
       <c r="B582" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E582" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>541</v>
       </c>
       <c r="B583" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="584" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E583" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>542</v>
       </c>
       <c r="B584" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="585" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E584" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>543</v>
       </c>
       <c r="B585" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="586" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E585" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>544</v>
       </c>
       <c r="B586" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="587" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E586" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>545</v>
       </c>
       <c r="B587" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="588" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E587" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>546</v>
       </c>
       <c r="B588" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="589" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E588" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>547</v>
       </c>
       <c r="B589" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E589" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>548</v>
       </c>
       <c r="B590" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E590" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>549</v>
       </c>
       <c r="B591" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E591" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>550</v>
       </c>
       <c r="B592" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E592" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>551</v>
       </c>
       <c r="B593" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E593" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>552</v>
       </c>
       <c r="B594" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E594" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>553</v>
       </c>
       <c r="B595" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E595" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>554</v>
       </c>
       <c r="B596" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="597" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E596" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>555</v>
       </c>
       <c r="B597" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="598" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E597" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>556</v>
       </c>
       <c r="B598" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="599" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E598" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>557</v>
       </c>
       <c r="B599" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="600" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E599" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>558</v>
       </c>
       <c r="B600" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="601" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E600" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>559</v>
       </c>
       <c r="B601" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="602" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E601" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>560</v>
       </c>
       <c r="B602" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="603" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E602" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>561</v>
       </c>
       <c r="B603" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="604" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E603" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>562</v>
       </c>
       <c r="B604" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="605" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E604" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>563</v>
       </c>
       <c r="B605" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E605" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>657</v>
       </c>
       <c r="B606" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="607" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E606" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>564</v>
       </c>
       <c r="B607" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E607" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>565</v>
       </c>
       <c r="B608" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="609" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E608" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>566</v>
       </c>
       <c r="B609" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E609" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>567</v>
       </c>
       <c r="B610" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E610" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>568</v>
       </c>
       <c r="B611" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E611" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>569</v>
       </c>
       <c r="B612" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E612" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>570</v>
       </c>
       <c r="B613" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="614" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E613" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>571</v>
       </c>
       <c r="B614" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E614" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>572</v>
       </c>
       <c r="B615" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="616" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E615" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>573</v>
       </c>
       <c r="B616" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="617" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E616" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>574</v>
       </c>
       <c r="B617" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="618" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E617" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>575</v>
       </c>
       <c r="B618" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="619" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E618" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>576</v>
       </c>
       <c r="B619" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="620" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E619" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>577</v>
       </c>
       <c r="B620" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="621" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E620" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>578</v>
       </c>
       <c r="B621" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="622" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E621" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>579</v>
       </c>
       <c r="B622" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="623" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E622" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>580</v>
       </c>
       <c r="B623" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E623" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>581</v>
       </c>
       <c r="B624" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="625" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E624" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>582</v>
       </c>
       <c r="B625" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E625" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>583</v>
       </c>
       <c r="B626" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E626" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>584</v>
       </c>
       <c r="B627" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E627" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>585</v>
       </c>
       <c r="B628" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="629" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E628" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>586</v>
       </c>
       <c r="B629" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="630" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E629" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>587</v>
       </c>
       <c r="B630" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="631" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E630" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>588</v>
       </c>
       <c r="B631" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="632" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E631" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>589</v>
       </c>
       <c r="B632" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E632" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>590</v>
       </c>
       <c r="B633" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E633" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>591</v>
       </c>
       <c r="B634" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="635" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E634" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>592</v>
       </c>
       <c r="B635" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="636" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E635" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>593</v>
       </c>
       <c r="B636" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="637" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E636" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>594</v>
       </c>
       <c r="B637" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="638" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E637" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>595</v>
       </c>
       <c r="B638" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="639" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E638" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>596</v>
       </c>
       <c r="B639" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="640" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E639" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>597</v>
       </c>
@@ -7835,133 +10471,201 @@
         <v>660</v>
       </c>
       <c r="C640" s="1"/>
-    </row>
-    <row r="641" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E640" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>598</v>
       </c>
       <c r="B641" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="642" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E641" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>599</v>
       </c>
       <c r="B642" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="643" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E642" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>600</v>
       </c>
       <c r="B643" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="644" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E643" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>601</v>
       </c>
       <c r="B644" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="645" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E644" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>602</v>
       </c>
       <c r="B645" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E645" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>603</v>
       </c>
       <c r="B646" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E646" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>604</v>
       </c>
       <c r="B647" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="648" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E647" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>605</v>
       </c>
       <c r="B648" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="649" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E648" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>606</v>
       </c>
       <c r="B649" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="650" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E649" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>607</v>
       </c>
       <c r="B650" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E650" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>608</v>
       </c>
       <c r="B651" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E651" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>609</v>
       </c>
       <c r="B652" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="653" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E652" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>610</v>
       </c>
       <c r="B653" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="654" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E653" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>611</v>
       </c>
       <c r="B654" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="655" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E654" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>612</v>
       </c>
       <c r="B655" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E655" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>613</v>
       </c>
       <c r="B656" t="s">
         <v>659</v>
+      </c>
+      <c r="E656" t="b">
+        <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37785BF8-B372-4E5C-9DDB-9ED951EA8BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51698AB-FD6A-4408-98BA-F7AFCD5301BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="744">
   <si>
     <t>taxon</t>
   </si>
@@ -2231,6 +2231,27 @@
   </si>
   <si>
     <t>www/media/fiches/pachygnatha_degeeri_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/episinus_maculipes_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/episinus_truncatus_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/euryopis_flavomaculata_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/neottiura_bimaculata_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/dipoena_melanogaster_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/episinus_maculipes_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/parasteatoda_lunata_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -9504,9 +9525,12 @@
       <c r="B552" t="s">
         <v>659</v>
       </c>
+      <c r="C552" t="s">
+        <v>741</v>
+      </c>
       <c r="E552" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -9636,9 +9660,15 @@
       <c r="B563" t="s">
         <v>659</v>
       </c>
+      <c r="C563" t="s">
+        <v>742</v>
+      </c>
+      <c r="D563" t="s">
+        <v>737</v>
+      </c>
       <c r="E563" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.3">
@@ -9648,9 +9678,12 @@
       <c r="B564" t="s">
         <v>659</v>
       </c>
+      <c r="D564" t="s">
+        <v>738</v>
+      </c>
       <c r="E564" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.3">
@@ -9660,9 +9693,12 @@
       <c r="B565" t="s">
         <v>659</v>
       </c>
+      <c r="D565" t="s">
+        <v>739</v>
+      </c>
       <c r="E565" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -9693,7 +9729,7 @@
       <c r="A568" t="s">
         <v>655</v>
       </c>
-      <c r="B568" t="s">
+      <c r="B568" s="2" t="s">
         <v>660</v>
       </c>
       <c r="E568" t="b">
@@ -9732,9 +9768,12 @@
       <c r="B571" t="s">
         <v>659</v>
       </c>
+      <c r="D571" t="s">
+        <v>740</v>
+      </c>
       <c r="E571" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.3">
@@ -9780,16 +9819,19 @@
       <c r="B575" t="s">
         <v>659</v>
       </c>
+      <c r="C575" t="s">
+        <v>743</v>
+      </c>
       <c r="E575" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>535</v>
       </c>
-      <c r="B576" t="s">
+      <c r="B576" s="2" t="s">
         <v>659</v>
       </c>
       <c r="E576" t="b">
@@ -9801,7 +9843,7 @@
       <c r="A577" t="s">
         <v>656</v>
       </c>
-      <c r="B577" t="s">
+      <c r="B577" s="2" t="s">
         <v>659</v>
       </c>
       <c r="E577" t="b">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96D43EF-FBFB-4EE7-8633-DE23702396A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000C2B9B-03EE-4EEC-A3C5-3183B521CE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="758">
   <si>
     <t>taxon</t>
   </si>
@@ -2279,6 +2279,21 @@
   </si>
   <si>
     <t>www/media/fiches/amaurobius_ferox_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/ebrechtella_tricuspidata_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/misumena_vatia_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/runcinia_grammica_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/ebrechtella_tricuspidata_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/misumena_vatia_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10320,9 +10335,15 @@
       <c r="B612" t="s">
         <v>659</v>
       </c>
+      <c r="C612" t="s">
+        <v>756</v>
+      </c>
+      <c r="D612" t="s">
+        <v>753</v>
+      </c>
       <c r="E612" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.3">
@@ -10356,9 +10377,15 @@
       <c r="B615" t="s">
         <v>659</v>
       </c>
+      <c r="C615" t="s">
+        <v>757</v>
+      </c>
+      <c r="D615" t="s">
+        <v>754</v>
+      </c>
       <c r="E615" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -10488,9 +10515,12 @@
       <c r="B626" t="s">
         <v>659</v>
       </c>
+      <c r="D626" t="s">
+        <v>755</v>
+      </c>
       <c r="E626" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F797E9-98D7-4177-98A1-AE25EACA31CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC1A586-EB9B-4117-9AD4-AE8BC006005A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="895">
   <si>
     <t>taxon</t>
   </si>
@@ -2700,6 +2700,12 @@
   </si>
   <si>
     <t>www/media/fiches/liocranum_rupicola_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/marpissa_nivoyi_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/marpissa_nivoyi_male.webp</t>
   </si>
 </sst>
 </file>
@@ -9480,7 +9486,13 @@
       </c>
       <c r="C491" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D491" t="s">
+        <v>893</v>
+      </c>
+      <c r="E491" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC1A586-EB9B-4117-9AD4-AE8BC006005A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BC08D4-6BC9-4471-ACFE-AB1138E16692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="896">
   <si>
     <t>taxon</t>
   </si>
@@ -2706,6 +2706,9 @@
   </si>
   <si>
     <t>www/media/fiches/marpissa_nivoyi_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/meta_menardi_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10014,7 +10017,10 @@
       </c>
       <c r="C531" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D531" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BC08D4-6BC9-4471-ACFE-AB1138E16692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D861E55-79CA-4C34-A0D9-6CE8B06C378B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="897">
   <si>
     <t>taxon</t>
   </si>
@@ -2709,6 +2709,9 @@
   </si>
   <si>
     <t>www/media/fiches/meta_menardi_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/micrommata_ligurina_male.webp</t>
   </si>
 </sst>
 </file>
@@ -9969,7 +9972,10 @@
       </c>
       <c r="C527" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E527" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D861E55-79CA-4C34-A0D9-6CE8B06C378B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9250224-4870-44D9-AB58-67E7823A281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="899">
   <si>
     <t>taxon</t>
   </si>
@@ -2712,6 +2712,12 @@
   </si>
   <si>
     <t>www/media/fiches/micrommata_ligurina_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/micrommata_virescens_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/micrommata_virescens_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -9987,7 +9993,13 @@
       </c>
       <c r="C528" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D528" t="s">
+        <v>898</v>
+      </c>
+      <c r="E528" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9250224-4870-44D9-AB58-67E7823A281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EF1FBC-DBBE-46D7-AB7E-6DA9926AA46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="900">
   <si>
     <t>taxon</t>
   </si>
@@ -2718,6 +2717,9 @@
   </si>
   <si>
     <t>www/media/fiches/micrommata_virescens_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/myrmarachne_formicaria_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -9540,7 +9542,10 @@
       </c>
       <c r="C494" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D494" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EF1FBC-DBBE-46D7-AB7E-6DA9926AA46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBB0F31-93C8-4807-912E-F5348EB64AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="901">
   <si>
     <t>taxon</t>
   </si>
@@ -2720,6 +2720,9 @@
   </si>
   <si>
     <t>www/media/fiches/myrmarachne_formicaria_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/nigma_puella_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -4595,7 +4598,10 @@
       </c>
       <c r="C106" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBB0F31-93C8-4807-912E-F5348EB64AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2237261D-A337-4F32-830C-3329B56A8FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="902">
   <si>
     <t>taxon</t>
   </si>
@@ -2723,6 +2723,9 @@
   </si>
   <si>
     <t>www/media/fiches/nigma_puella_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/pachygnatha_clercki_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10109,7 +10112,10 @@
       </c>
       <c r="C535" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D535" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2237261D-A337-4F32-830C-3329B56A8FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF227168-C1A5-442A-8DD3-9965EAAA4698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="903">
   <si>
     <t>taxon</t>
   </si>
@@ -2726,6 +2726,9 @@
   </si>
   <si>
     <t>www/media/fiches/pachygnatha_clercki_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/pachygnatha_listeri_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10145,7 +10148,10 @@
       </c>
       <c r="C537" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D537" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF227168-C1A5-442A-8DD3-9965EAAA4698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB95639-E120-4896-A4E8-56FA0A381C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="904">
   <si>
     <t>taxon</t>
   </si>
@@ -2729,6 +2730,9 @@
   </si>
   <si>
     <t>www/media/fiches/pachygnatha_listeri_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/pistius_truncatus_male.webp</t>
   </si>
 </sst>
 </file>
@@ -11330,7 +11334,10 @@
       </c>
       <c r="C624" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E624" t="s">
+        <v>903</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB95639-E120-4896-A4E8-56FA0A381C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BD817F-9384-43BE-B89F-8F1B8CEAC3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="906">
   <si>
     <t>taxon</t>
   </si>
@@ -2733,6 +2733,12 @@
   </si>
   <si>
     <t>www/media/fiches/pistius_truncatus_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/philaeus_chrysops_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/philaeus_chrysops_male.webp</t>
   </si>
 </sst>
 </file>
@@ -9669,7 +9675,13 @@
       </c>
       <c r="C503" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D503" t="s">
+        <v>904</v>
+      </c>
+      <c r="E503" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BD817F-9384-43BE-B89F-8F1B8CEAC3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643D89C2-C19C-4A29-91BE-3729DB524B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="907">
   <si>
     <t>taxon</t>
   </si>
@@ -2739,6 +2739,9 @@
   </si>
   <si>
     <t>www/media/fiches/philaeus_chrysops_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/philodromus_margaritatus_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -8835,7 +8838,10 @@
       </c>
       <c r="C441" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D441" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643D89C2-C19C-4A29-91BE-3729DB524B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F3E554-307D-483C-82F6-1882D2853FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="908">
   <si>
     <t>taxon</t>
   </si>
@@ -2742,6 +2742,9 @@
   </si>
   <si>
     <t>www/media/fiches/philodromus_margaritatus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/pirata_piraticus_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -8340,7 +8343,10 @@
       </c>
       <c r="C403" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F3E554-307D-483C-82F6-1882D2853FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166AA76D-8B17-4E91-A943-030C5E7812F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="909">
   <si>
     <t>taxon</t>
   </si>
@@ -2745,6 +2745,9 @@
   </si>
   <si>
     <t>www/media/fiches/pirata_piraticus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/poecilochroa_variana_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -5160,7 +5163,10 @@
       </c>
       <c r="C149" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D149" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166AA76D-8B17-4E91-A943-030C5E7812F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBD2F2F-74B0-419D-B307-69DC6DD8F804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="910">
   <si>
     <t>taxon</t>
   </si>
@@ -2748,6 +2748,9 @@
   </si>
   <si>
     <t>www/media/fiches/poecilochroa_variana_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/textrix_denticulata_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -3422,7 +3425,10 @@
       </c>
       <c r="C18" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBD2F2F-74B0-419D-B307-69DC6DD8F804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CFEB7F-33D8-405E-B0CA-043E7BABC96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="911">
   <si>
     <t>taxon</t>
   </si>
@@ -2751,6 +2751,9 @@
   </si>
   <si>
     <t>www/media/fiches/textrix_denticulata_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/steatoda_albomaculata_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10920,7 +10923,10 @@
       </c>
       <c r="C591" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D591" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CFEB7F-33D8-405E-B0CA-043E7BABC96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F0A3BC-5B9C-4A0B-9229-D848ABF00434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="912">
   <si>
     <t>taxon</t>
   </si>
@@ -2754,6 +2754,9 @@
   </si>
   <si>
     <t>www/media/fiches/steatoda_albomaculata_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/theridiosoma_gemmosum_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -11124,7 +11127,10 @@
       </c>
       <c r="C606" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D606" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F0A3BC-5B9C-4A0B-9229-D848ABF00434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3F961E-688C-4007-BF19-9D66E9498986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="913">
   <si>
     <t>taxon</t>
   </si>
@@ -2757,6 +2757,9 @@
   </si>
   <si>
     <t>www/media/fiches/theridiosoma_gemmosum_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/thomisus_onustus_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -11445,7 +11448,10 @@
       </c>
       <c r="C628" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D628" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3F961E-688C-4007-BF19-9D66E9498986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB02A2F-4A33-4BBE-93A0-611AEEFE458B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="914">
   <si>
     <t>taxon</t>
   </si>
@@ -2760,6 +2759,9 @@
   </si>
   <si>
     <t>www/media/fiches/thomisus_onustus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/salticus_mutabilis_male.webp</t>
   </si>
 </sst>
 </file>
@@ -9848,6 +9850,9 @@
       <c r="D512" t="s">
         <v>725</v>
       </c>
+      <c r="E512" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" t="s">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB02A2F-4A33-4BBE-93A0-611AEEFE458B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA20695-8B3B-4C89-9F0F-F30A30C7E9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="915">
   <si>
     <t>taxon</t>
   </si>
@@ -2762,6 +2762,9 @@
   </si>
   <si>
     <t>www/media/fiches/salticus_mutabilis_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/xysticus_ulmi_male.webp</t>
   </si>
 </sst>
 </file>
@@ -11704,6 +11707,9 @@
       <c r="D646" t="s">
         <v>760</v>
       </c>
+      <c r="E646" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" t="s">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA20695-8B3B-4C89-9F0F-F30A30C7E9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CCAF73-1A2A-4E70-9031-218293692B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="916">
   <si>
     <t>taxon</t>
   </si>
@@ -2765,6 +2765,9 @@
   </si>
   <si>
     <t>www/media/fiches/xysticus_ulmi_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/amaurobius_similis_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -3499,7 +3502,10 @@
       </c>
       <c r="C22" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CCAF73-1A2A-4E70-9031-218293692B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F92241-7D7D-4793-A4E3-6C03EF51F113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="917">
   <si>
     <t>taxon</t>
   </si>
@@ -2768,6 +2768,9 @@
   </si>
   <si>
     <t>www/media/fiches/amaurobius_similis_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/aculepeira_ceropegia_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -3559,7 +3562,10 @@
       </c>
       <c r="C26" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F92241-7D7D-4793-A4E3-6C03EF51F113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C696FB-A4E2-4DFA-ADED-1DBC9992E1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="918">
   <si>
     <t>taxon</t>
   </si>
@@ -2771,6 +2771,9 @@
   </si>
   <si>
     <t>www/media/fiches/aculepeira_ceropegia_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/atypus_affinis_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -4088,7 +4091,10 @@
       </c>
       <c r="C63" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C696FB-A4E2-4DFA-ADED-1DBC9992E1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E46A5E-F33A-476B-8517-D5942CA5A250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="919">
   <si>
     <t>taxon</t>
   </si>
@@ -2774,6 +2774,9 @@
   </si>
   <si>
     <t>www/media/fiches/atypus_affinis_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/atypus_piceus_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -4106,7 +4109,10 @@
       </c>
       <c r="C64" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E46A5E-F33A-476B-8517-D5942CA5A250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20A68C8-40D0-4A74-A774-0F32F1166FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="920">
   <si>
     <t>taxon</t>
   </si>
@@ -2777,6 +2777,9 @@
   </si>
   <si>
     <t>www/media/fiches/atypus_piceus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/cercidia_prominens_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -3771,6 +3774,9 @@
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
         <v>1</v>
       </c>
+      <c r="D39" t="s">
+        <v>919</v>
+      </c>
       <c r="E39" t="s">
         <v>684</v>
       </c>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20A68C8-40D0-4A74-A774-0F32F1166FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F1BD9-81FE-446D-85E9-340C4CF32D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="921">
   <si>
     <t>taxon</t>
   </si>
@@ -2777,6 +2777,9 @@
   </si>
   <si>
     <t>www/media/fiches/atypus_piceus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/cicurina_cicur_femelle.webp</t>
   </si>
   <si>
     <t>www/media/fiches/cercidia_prominens_femelle.webp</t>
@@ -3775,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E39" t="s">
         <v>684</v>
@@ -5360,7 +5363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>152</v>
       </c>
@@ -5372,7 +5375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>153</v>
       </c>
@@ -5381,10 +5384,13 @@
       </c>
       <c r="C162" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D162" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>154</v>
       </c>
@@ -5396,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>155</v>
       </c>
@@ -5408,7 +5414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>156</v>
       </c>
@@ -5420,7 +5426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>157</v>
       </c>
@@ -5432,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>158</v>
       </c>
@@ -5444,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>159</v>
       </c>
@@ -5456,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>160</v>
       </c>
@@ -5468,7 +5474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>161</v>
       </c>
@@ -5480,7 +5486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>162</v>
       </c>
@@ -5492,7 +5498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>163</v>
       </c>
@@ -5504,7 +5510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>164</v>
       </c>
@@ -5516,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>165</v>
       </c>
@@ -5528,7 +5534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>166</v>
       </c>
@@ -5540,7 +5546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>167</v>
       </c>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F1BD9-81FE-446D-85E9-340C4CF32D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9155CCE6-C110-44FA-BD5A-27031C136273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="923">
   <si>
     <t>taxon</t>
   </si>
@@ -2782,7 +2782,13 @@
     <t>www/media/fiches/cicurina_cicur_femelle.webp</t>
   </si>
   <si>
+    <t>www/media/fiches/crustulina_guttata_femelle.webp</t>
+  </si>
+  <si>
     <t>www/media/fiches/cercidia_prominens_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/crustulina_guttata_male.webp</t>
   </si>
 </sst>
 </file>
@@ -3778,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E39" t="s">
         <v>684</v>
@@ -10397,7 +10403,13 @@
       </c>
       <c r="C548" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D548" t="s">
+        <v>920</v>
+      </c>
+      <c r="E548" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9155CCE6-C110-44FA-BD5A-27031C136273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AADEE14-43CC-4D3C-83A9-EE3DF64B69E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="924">
   <si>
     <t>taxon</t>
   </si>
@@ -2777,6 +2777,9 @@
   </si>
   <si>
     <t>www/media/fiches/atypus_piceus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/dysdera_erythrina_femelle.webp</t>
   </si>
   <si>
     <t>www/media/fiches/cicurina_cicur_femelle.webp</t>
@@ -3784,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E39" t="s">
         <v>684</v>
@@ -4727,7 +4730,10 @@
       </c>
       <c r="C109" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D109" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -5393,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -10406,10 +10412,10 @@
         <v>1</v>
       </c>
       <c r="D548" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E548" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AADEE14-43CC-4D3C-83A9-EE3DF64B69E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AA93CD-30B2-4879-99F3-FA7CF9AC354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="925">
   <si>
     <t>taxon</t>
   </si>
@@ -2792,6 +2792,9 @@
   </si>
   <si>
     <t>www/media/fiches/crustulina_guttata_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/episinus_angulatus_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10604,7 +10607,10 @@
       </c>
       <c r="C562" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D562" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AA93CD-30B2-4879-99F3-FA7CF9AC354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8B764A-A7EA-4E84-BC3B-EF41A26661C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="926">
   <si>
     <t>taxon</t>
   </si>
@@ -2795,6 +2795,9 @@
   </si>
   <si>
     <t>www/media/fiches/episinus_angulatus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/heliophanus_kochii_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -9515,7 +9518,10 @@
       </c>
       <c r="C485" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D485" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8B764A-A7EA-4E84-BC3B-EF41A26661C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BACCE5-0C7C-4BF9-AA4E-EC599A64557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="927">
   <si>
     <t>taxon</t>
   </si>
@@ -2798,6 +2798,9 @@
   </si>
   <si>
     <t>www/media/fiches/heliophanus_kochii_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/kochiura_aulica_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -10718,7 +10721,10 @@
       </c>
       <c r="C569" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D569" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BACCE5-0C7C-4BF9-AA4E-EC599A64557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4166A705-4307-441C-9CA7-A21CA6E66A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="929">
   <si>
     <t>taxon</t>
   </si>
@@ -2801,6 +2801,12 @@
   </si>
   <si>
     <t>www/media/fiches/kochiura_aulica_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/neoscona_adianta_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/neriene_emphana_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -4024,7 +4030,10 @@
       </c>
       <c r="C56" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -6824,7 +6833,10 @@
       </c>
       <c r="C275" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D275" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4166A705-4307-441C-9CA7-A21CA6E66A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87765C43-FFB9-4F01-9860-976FB32C87D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="930">
   <si>
     <t>taxon</t>
   </si>
@@ -2807,6 +2807,9 @@
   </si>
   <si>
     <t>www/media/fiches/neriene_emphana_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/olios_argelasius_male.webp</t>
   </si>
 </sst>
 </file>
@@ -10157,7 +10160,10 @@
       </c>
       <c r="C529" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E529" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87765C43-FFB9-4F01-9860-976FB32C87D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B388F3-C144-414C-AA31-930F65B47513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="931">
   <si>
     <t>taxon</t>
   </si>
@@ -2810,6 +2810,9 @@
   </si>
   <si>
     <t>www/media/fiches/olios_argelasius_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/oxyopes_heterophthalmus_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -8783,7 +8786,10 @@
       </c>
       <c r="C430" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>930</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B388F3-C144-414C-AA31-930F65B47513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6690D22-0AF3-480A-A7A1-FB811976DB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="932">
   <si>
     <t>taxon</t>
   </si>
@@ -2813,6 +2813,9 @@
   </si>
   <si>
     <t>www/media/fiches/oxyopes_heterophthalmus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/oxyopes_ramosus_femelle.xebp</t>
   </si>
 </sst>
 </file>
@@ -8828,7 +8831,10 @@
       </c>
       <c r="C433" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D433" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6690D22-0AF3-480A-A7A1-FB811976DB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3379BD25-6EAF-40C3-9E50-E352A89220B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2815,7 +2815,7 @@
     <t>www/media/fiches/oxyopes_heterophthalmus_femelle.webp</t>
   </si>
   <si>
-    <t>www/media/fiches/oxyopes_ramosus_femelle.xebp</t>
+    <t>www/media/fiches/oxyopes_ramosus_femelle.webp</t>
   </si>
 </sst>
 </file>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3379BD25-6EAF-40C3-9E50-E352A89220B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B6CA45-781A-49B5-B5FA-B38EC70C575B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="933">
   <si>
     <t>taxon</t>
   </si>
@@ -2816,6 +2816,9 @@
   </si>
   <si>
     <t>www/media/fiches/oxyopes_ramosus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/porrhomma_pygmaeum_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -7250,7 +7253,10 @@
       </c>
       <c r="C307" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D307" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B6CA45-781A-49B5-B5FA-B38EC70C575B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C8D710-B035-4576-B84A-24746F07EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="934">
   <si>
     <t>taxon</t>
   </si>
@@ -2819,6 +2819,9 @@
   </si>
   <si>
     <t>www/media/fiches/porrhomma_pygmaeum_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/araneus_sturmi_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -3718,7 +3721,10 @@
       </c>
       <c r="C33" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C8D710-B035-4576-B84A-24746F07EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FFB1AF-4073-4725-A3AD-7C65332BB81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="935">
   <si>
     <t>taxon</t>
   </si>
@@ -2491,9 +2491,6 @@
     <t>www/media/fiches/tibellus_oblongus_male.webp</t>
   </si>
   <si>
-    <t>www/media/fiches/salticus_zebraenus_male.webp</t>
-  </si>
-  <si>
     <t>www/media/fiches/tetragnatha_extensa_male.webp</t>
   </si>
   <si>
@@ -2822,6 +2819,12 @@
   </si>
   <si>
     <t>www/media/fiches/araneus_sturmi_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/salticus_zebraneus_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/salticus_zebraneus_male.webp</t>
   </si>
 </sst>
 </file>
@@ -3400,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -3499,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -3526,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -3559,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -3616,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -3631,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -3646,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -3661,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -3724,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -3739,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -3805,7 +3808,7 @@
         <v>683</v>
       </c>
       <c r="E38" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -3820,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E39" t="s">
         <v>684</v>
@@ -3865,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -3907,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -4051,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -4151,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -4166,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -4361,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -4490,7 +4493,7 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E89" t="s">
         <v>771</v>
@@ -4649,7 +4652,7 @@
         <v>772</v>
       </c>
       <c r="E101" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -4676,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E103" t="s">
         <v>773</v>
@@ -4724,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -4769,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -4862,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -5267,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -5282,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E150" t="s">
         <v>776</v>
@@ -5312,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -5435,7 +5438,7 @@
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -6218,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
@@ -6839,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
@@ -6854,7 +6857,7 @@
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
@@ -6893,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E278" t="s">
         <v>675</v>
@@ -7235,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -7262,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -8018,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="E369" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
@@ -8069,7 +8072,7 @@
         <v>1</v>
       </c>
       <c r="E373" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
@@ -8084,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
@@ -8195,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="D383" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
@@ -8237,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="E386" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
@@ -8252,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="D387" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
@@ -8267,7 +8270,7 @@
         <v>1</v>
       </c>
       <c r="D388" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
@@ -8318,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E392" t="s">
         <v>796</v>
@@ -8396,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="E398" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
@@ -8435,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="E401" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.3">
@@ -8462,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="D403" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.3">
@@ -8477,7 +8480,7 @@
         <v>1</v>
       </c>
       <c r="D404" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.3">
@@ -8702,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="D422" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
@@ -8804,7 +8807,7 @@
         <v>1</v>
       </c>
       <c r="D430" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
@@ -8819,7 +8822,7 @@
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
@@ -8846,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="D433" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
@@ -8882,7 +8885,7 @@
         <v>801</v>
       </c>
       <c r="E435" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
@@ -8969,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="D441" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
@@ -9023,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="D445" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
@@ -9194,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="D458" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E458" t="s">
         <v>705</v>
@@ -9290,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="D465" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
@@ -9383,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="D472" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
@@ -9458,7 +9461,7 @@
         <v>715</v>
       </c>
       <c r="E477" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
@@ -9563,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="D485" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
@@ -9662,10 +9665,10 @@
         <v>1</v>
       </c>
       <c r="D491" t="s">
+        <v>892</v>
+      </c>
+      <c r="E491" t="s">
         <v>893</v>
-      </c>
-      <c r="E491" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
@@ -9704,7 +9707,7 @@
         <v>1</v>
       </c>
       <c r="D494" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
@@ -9815,10 +9818,10 @@
         <v>1</v>
       </c>
       <c r="D503" t="s">
+        <v>903</v>
+      </c>
+      <c r="E503" t="s">
         <v>904</v>
-      </c>
-      <c r="E503" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
@@ -9863,7 +9866,7 @@
         <v>804</v>
       </c>
       <c r="E506" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.3">
@@ -9881,7 +9884,7 @@
         <v>805</v>
       </c>
       <c r="E507" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
@@ -9953,7 +9956,7 @@
         <v>725</v>
       </c>
       <c r="E512" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.3">
@@ -9968,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="D513" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E513" t="s">
         <v>731</v>
@@ -9985,8 +9988,11 @@
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
         <v>1</v>
       </c>
+      <c r="D514" t="s">
+        <v>933</v>
+      </c>
       <c r="E514" t="s">
-        <v>823</v>
+        <v>934</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.3">
@@ -10154,7 +10160,7 @@
         <v>1</v>
       </c>
       <c r="E527" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.3">
@@ -10169,10 +10175,10 @@
         <v>1</v>
       </c>
       <c r="D528" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E528" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
@@ -10187,7 +10193,7 @@
         <v>1</v>
       </c>
       <c r="E529" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.3">
@@ -10214,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="D531" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.3">
@@ -10277,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="D535" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.3">
@@ -10292,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="D536" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E536" t="s">
         <v>736</v>
@@ -10310,7 +10316,7 @@
         <v>1</v>
       </c>
       <c r="D537" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.3">
@@ -10343,7 +10349,7 @@
         <v>807</v>
       </c>
       <c r="E539" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.3">
@@ -10361,7 +10367,7 @@
         <v>808</v>
       </c>
       <c r="E540" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.3">
@@ -10376,7 +10382,7 @@
         <v>1</v>
       </c>
       <c r="D541" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.3">
@@ -10451,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="E547" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.3">
@@ -10466,10 +10472,10 @@
         <v>1</v>
       </c>
       <c r="D548" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E548" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.3">
@@ -10586,10 +10592,10 @@
         <v>1</v>
       </c>
       <c r="D557" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E557" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.3">
@@ -10604,7 +10610,7 @@
         <v>1</v>
       </c>
       <c r="E558" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.3">
@@ -10622,7 +10628,7 @@
         <v>810</v>
       </c>
       <c r="E559" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.3">
@@ -10661,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="D562" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.3">
@@ -10751,7 +10757,7 @@
         <v>811</v>
       </c>
       <c r="E568" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.3">
@@ -10766,7 +10772,7 @@
         <v>1</v>
       </c>
       <c r="D569" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.3">
@@ -11027,7 +11033,7 @@
         <v>813</v>
       </c>
       <c r="E589" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.3">
@@ -11054,7 +11060,7 @@
         <v>1</v>
       </c>
       <c r="D591" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.3">
@@ -11129,7 +11135,7 @@
         <v>1</v>
       </c>
       <c r="D596" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.3">
@@ -11204,7 +11210,7 @@
         <v>1</v>
       </c>
       <c r="E602" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.3">
@@ -11255,7 +11261,7 @@
         <v>1</v>
       </c>
       <c r="D606" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.3">
@@ -11354,7 +11360,7 @@
         <v>1</v>
       </c>
       <c r="D613" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.3">
@@ -11423,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="E618" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.3">
@@ -11441,7 +11447,7 @@
         <v>814</v>
       </c>
       <c r="E619" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.3">
@@ -11468,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="E621" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.3">
@@ -11495,7 +11501,7 @@
         <v>1</v>
       </c>
       <c r="E623" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.3">
@@ -11510,7 +11516,7 @@
         <v>1</v>
       </c>
       <c r="E624" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.3">
@@ -11537,7 +11543,7 @@
         <v>1</v>
       </c>
       <c r="D626" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E626" t="s">
         <v>755</v>
@@ -11558,7 +11564,7 @@
         <v>759</v>
       </c>
       <c r="E627" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.3">
@@ -11573,7 +11579,7 @@
         <v>1</v>
       </c>
       <c r="D628" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.3">
@@ -11588,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="E629" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.3">
@@ -11618,7 +11624,7 @@
         <v>815</v>
       </c>
       <c r="E631" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.3">
@@ -11720,7 +11726,7 @@
         <v>1</v>
       </c>
       <c r="E639" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.3">
@@ -11738,7 +11744,7 @@
         <v>817</v>
       </c>
       <c r="E640" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.3">
@@ -11780,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="E643" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.3">
@@ -11822,7 +11828,7 @@
         <v>760</v>
       </c>
       <c r="E646" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.3">
@@ -11924,10 +11930,10 @@
         <v>1</v>
       </c>
       <c r="D654" t="s">
+        <v>838</v>
+      </c>
+      <c r="E654" t="s">
         <v>839</v>
-      </c>
-      <c r="E654" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FFB1AF-4073-4725-A3AD-7C65332BB81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2AFC21-5582-46EB-887F-C3F185F11F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="936">
   <si>
     <t>taxon</t>
   </si>
@@ -2825,6 +2825,9 @@
   </si>
   <si>
     <t>www/media/fiches/salticus_zebraneus_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/theridion_varians_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -11246,7 +11249,10 @@
       </c>
       <c r="C605" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D605" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2AFC21-5582-46EB-887F-C3F185F11F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED064EE0-6103-42E3-A9C8-5A41E70B051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="937">
   <si>
     <t>taxon</t>
   </si>
@@ -2828,6 +2828,9 @@
   </si>
   <si>
     <t>www/media/fiches/theridion_varians_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/cyclosa_conica_male.webp</t>
   </si>
 </sst>
 </file>
@@ -3846,6 +3849,9 @@
       <c r="D40" t="s">
         <v>685</v>
       </c>
+      <c r="E40" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED064EE0-6103-42E3-A9C8-5A41E70B051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB3ABAC-DF59-417E-BD39-094C7BA00F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="938">
   <si>
     <t>taxon</t>
   </si>
@@ -2831,6 +2831,9 @@
   </si>
   <si>
     <t>www/media/fiches/cyclosa_conica_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/oonops_domesticus_male.webp</t>
   </si>
 </sst>
 </file>
@@ -8639,7 +8642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>386</v>
       </c>
@@ -8654,7 +8657,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>387</v>
       </c>
@@ -8666,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>388</v>
       </c>
@@ -8678,7 +8681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>389</v>
       </c>
@@ -8690,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>390</v>
       </c>
@@ -8702,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>391</v>
       </c>
@@ -8717,7 +8720,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>392</v>
       </c>
@@ -8729,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>393</v>
       </c>
@@ -8741,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>646</v>
       </c>
@@ -8753,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>394</v>
       </c>
@@ -8767,8 +8770,11 @@
       <c r="D426" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E426" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>395</v>
       </c>
@@ -8780,7 +8786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>396</v>
       </c>
@@ -8792,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>397</v>
       </c>
@@ -8804,7 +8810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>647</v>
       </c>
@@ -8819,7 +8825,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>398</v>
       </c>
@@ -8834,7 +8840,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>399</v>
       </c>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB3ABAC-DF59-417E-BD39-094C7BA00F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153575E6-E57C-4C2B-852D-B7EBCD5E9656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="939">
   <si>
     <t>taxon</t>
   </si>
@@ -2834,6 +2834,9 @@
   </si>
   <si>
     <t>www/media/fiches/oonops_domesticus_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/tetragnatha_obtusa_male.webp</t>
   </si>
 </sst>
 </file>
@@ -10409,7 +10412,10 @@
       </c>
       <c r="C542" t="b">
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E542" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.3">

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153575E6-E57C-4C2B-852D-B7EBCD5E9656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A078F2CC-947F-47A8-9C0E-E4F72EDA0CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="940">
   <si>
     <t>taxon</t>
   </si>
@@ -2837,6 +2837,9 @@
   </si>
   <si>
     <t>www/media/fiches/tetragnatha_obtusa_male.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/ballus_chalybeius_femelle.webp</t>
   </si>
 </sst>
 </file>
@@ -9388,6 +9391,9 @@
         <f>OR(Tableau1[[#This Row],[femelle]]&lt;&gt;"", Tableau1[[#This Row],[male]]&lt;&gt;"")</f>
         <v>1</v>
       </c>
+      <c r="D471" t="s">
+        <v>939</v>
+      </c>
       <c r="E471" t="s">
         <v>708</v>
       </c>

--- a/photos.xlsx
+++ b/photos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cedri\Documents\web\araignees_idf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A078F2CC-947F-47A8-9C0E-E4F72EDA0CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848937A7-E66A-4E16-A932-12D51223513F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="941">
   <si>
     <t>taxon</t>
   </si>
@@ -2840,6 +2840,9 @@
   </si>
   <si>
     <t>www/media/fiches/ballus_chalybeius_femelle.webp</t>
+  </si>
+  <si>
+    <t>www/media/fiches/civizelotes_civicus_male.webp</t>
   </si>
 </sst>
 </file>
@@ -4885,6 +4888,9 @@
       <c r="D116" t="s">
         <v>850</v>
       </c>
+      <c r="E116" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
